--- a/Team-Data/2013-14/2-8-2013-14.xlsx
+++ b/Team-Data/2013-14/2-8-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.51</v>
+        <v>0.521</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J2" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.461</v>
@@ -688,37 +755,37 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.784</v>
       </c>
       <c r="R2" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="V2" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
@@ -727,19 +794,19 @@
         <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.1</v>
+        <v>102.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -748,22 +815,22 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI2" t="n">
         <v>13</v>
       </c>
-      <c r="AH2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>14</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
@@ -772,19 +839,19 @@
         <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -805,10 +872,10 @@
         <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -939,7 +1006,7 @@
         <v>24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
         <v>25</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
@@ -966,7 +1033,7 @@
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -975,13 +1042,13 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1118,13 +1185,13 @@
         <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>14</v>
@@ -1133,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1154,7 +1221,7 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.431</v>
+        <v>0.44</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K5" t="n">
         <v>0.435</v>
@@ -1243,28 +1310,28 @@
         <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
         <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
         <v>33</v>
       </c>
       <c r="T5" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X5" t="n">
         <v>5</v>
@@ -1276,16 +1343,16 @@
         <v>18.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,13 +1364,13 @@
         <v>20</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1324,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1333,10 +1400,10 @@
         <v>8</v>
       </c>
       <c r="AT5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU5" t="n">
         <v>22</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>23</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>-0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
@@ -1500,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
@@ -1521,7 +1588,7 @@
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>25</v>
@@ -1682,7 +1749,7 @@
         <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>19</v>
@@ -1706,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1718,7 +1785,7 @@
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1837,10 +1904,10 @@
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>28</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J9" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.452</v>
       </c>
       <c r="L9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.363</v>
+        <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="R9" t="n">
         <v>12.1</v>
       </c>
       <c r="S9" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T9" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
         <v>22.2</v>
       </c>
       <c r="V9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
         <v>5.8</v>
@@ -2001,25 +2068,25 @@
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.8</v>
+        <v>103.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
         <v>14</v>
@@ -2028,7 +2095,7 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
@@ -2037,31 +2104,31 @@
         <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2070,7 +2137,7 @@
         <v>22</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2082,13 +2149,13 @@
         <v>28</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2184,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.42</v>
+        <v>0.408</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
         <v>19.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.312</v>
+        <v>0.31</v>
       </c>
       <c r="O10" t="n">
         <v>17.3</v>
@@ -2156,22 +2223,22 @@
         <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.666</v>
+        <v>0.664</v>
       </c>
       <c r="R10" t="n">
         <v>14.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W10" t="n">
         <v>8.9</v>
@@ -2186,28 +2253,28 @@
         <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.6</v>
+        <v>100.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>9</v>
@@ -2216,13 +2283,13 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2264,7 +2331,7 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -2299,94 +2366,94 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.588</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J11" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O11" t="n">
         <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R11" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="T11" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="U11" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
         <v>5.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.1</v>
+        <v>102.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>19</v>
@@ -2398,22 +2465,22 @@
         <v>6</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
         <v>25</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
@@ -2437,16 +2504,16 @@
         <v>14</v>
       </c>
       <c r="AX11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY11" t="n">
         <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
       </c>
       <c r="AZ11" t="n">
         <v>24</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.66</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J12" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.473</v>
@@ -2514,31 +2581,31 @@
         <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="P12" t="n">
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0.6889999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T12" t="n">
-        <v>44.7</v>
+        <v>44.9</v>
       </c>
       <c r="U12" t="n">
         <v>20.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
@@ -2547,19 +2614,19 @@
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.3</v>
+        <v>105.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2568,7 +2635,7 @@
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2592,7 +2659,7 @@
         <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2616,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2634,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>20</v>
@@ -2780,7 +2847,7 @@
         <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2792,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -2926,13 +2993,13 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>22</v>
@@ -2956,7 +3023,7 @@
         <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -3141,10 +3208,10 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
@@ -3153,13 +3220,13 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
         <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
         <v>22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.551</v>
+        <v>0.542</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,10 +3294,10 @@
         <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K16" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
@@ -3242,52 +3309,52 @@
         <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="P16" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0.747</v>
       </c>
       <c r="R16" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3305,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
@@ -3317,10 +3384,10 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
         <v>27</v>
@@ -3344,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>19</v>
@@ -3356,13 +3423,13 @@
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -3391,61 +3458,61 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>0.714</v>
+        <v>0.729</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.508</v>
+        <v>0.509</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
         <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="S17" t="n">
         <v>29.4</v>
       </c>
       <c r="T17" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="U17" t="n">
         <v>23.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W17" t="n">
         <v>9.1</v>
@@ -3457,34 +3524,34 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104</v>
+        <v>104.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
       </c>
       <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI17" t="n">
         <v>4</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,22 +3560,22 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,13 +3590,13 @@
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
         <v>8</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
         <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>0.18</v>
+        <v>0.184</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
       </c>
       <c r="I18" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.421</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.754</v>
@@ -3618,13 +3685,13 @@
         <v>11.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -3642,16 +3709,16 @@
         <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.5</v>
+        <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3681,10 +3748,10 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3702,7 +3769,7 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
@@ -3717,10 +3784,10 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA18" t="n">
         <v>17</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.471</v>
+        <v>0.48</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,46 +3840,46 @@
         <v>38.4</v>
       </c>
       <c r="J19" t="n">
-        <v>88</v>
+        <v>87.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R19" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
         <v>33</v>
       </c>
       <c r="T19" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>3.6</v>
@@ -3821,25 +3888,25 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.6</v>
+        <v>105.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>17</v>
@@ -3875,16 +3942,16 @@
         <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
         <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>7</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>1</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
         <v>19</v>
@@ -4030,7 +4097,7 @@
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4054,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
         <v>5</v>
@@ -4084,7 +4151,7 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>17</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>22</v>
@@ -4215,7 +4282,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>19</v>
@@ -4227,7 +4294,7 @@
         <v>7</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4257,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4394,10 +4461,10 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4448,10 +4515,10 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4597,7 +4664,7 @@
         <v>22</v>
       </c>
       <c r="AP23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>14</v>
@@ -4609,7 +4676,7 @@
         <v>12</v>
       </c>
       <c r="AT23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4828,7 @@
         <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
         <v>22</v>
@@ -4791,7 +4858,7 @@
         <v>10</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>11</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.369</v>
+        <v>0.366</v>
       </c>
       <c r="O25" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P25" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
@@ -4895,13 +4962,13 @@
         <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U25" t="n">
         <v>19.1</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
         <v>8.300000000000001</v>
@@ -4919,22 +4986,22 @@
         <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.1</v>
+        <v>104.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -4946,16 +5013,16 @@
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>11</v>
@@ -4997,7 +5064,7 @@
         <v>10</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
         <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.706</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,10 +5114,10 @@
         <v>39.8</v>
       </c>
       <c r="J26" t="n">
-        <v>88.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
@@ -5059,22 +5126,22 @@
         <v>24.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T26" t="n">
         <v>46.5</v>
@@ -5086,28 +5153,28 @@
         <v>13.7</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>108</v>
+        <v>107.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5119,13 +5186,13 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
@@ -5140,16 +5207,16 @@
         <v>3</v>
       </c>
       <c r="AO26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
         <v>5</v>
@@ -5167,13 +5234,13 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5313,7 +5380,7 @@
         <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
         <v>24</v>
@@ -5346,13 +5413,13 @@
         <v>14</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.725</v>
+        <v>0.72</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.489</v>
+        <v>0.49</v>
       </c>
       <c r="L28" t="n">
         <v>8.1</v>
@@ -5426,19 +5493,19 @@
         <v>0.393</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.773</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
         <v>42.4</v>
@@ -5456,10 +5523,10 @@
         <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
@@ -5468,19 +5535,19 @@
         <v>103.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
         <v>19</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5504,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5528,7 +5595,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>2</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>9</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>2.3</v>
       </c>
       <c r="AD29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF29" t="n">
         <v>13</v>
       </c>
-      <c r="AE29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>12</v>
-      </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
@@ -5677,13 +5744,13 @@
         <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
@@ -5692,10 +5759,10 @@
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS29" t="n">
         <v>20</v>
@@ -5704,7 +5771,7 @@
         <v>13</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
         <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5775,31 +5842,31 @@
         <v>35.6</v>
       </c>
       <c r="J30" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L30" t="n">
         <v>6.7</v>
       </c>
       <c r="M30" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P30" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.748</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
         <v>30.5</v>
@@ -5817,34 +5884,34 @@
         <v>6.8</v>
       </c>
       <c r="X30" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y30" t="n">
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.6</v>
+        <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF30" t="n">
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH30" t="n">
         <v>23</v>
@@ -5853,13 +5920,13 @@
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
@@ -5868,19 +5935,19 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS30" t="n">
         <v>24</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5895,13 +5962,13 @@
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>1</v>
@@ -6068,7 +6135,7 @@
         <v>17</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
         <v>16</v>
@@ -6077,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6086,7 +6153,7 @@
         <v>15</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-8-2013-14</t>
+          <t>2014-02-08</t>
         </is>
       </c>
     </row>
